--- a/Organization_Template.xlsx
+++ b/Organization_Template.xlsx
@@ -15,8 +15,7 @@
     <sheet name="Contact people" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Interfaces" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Vendor info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Notes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Accounts" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Accounts" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -677,36 +676,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16.140625" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Organization_Template.xlsx
+++ b/Organization_Template.xlsx
@@ -12,10 +12,11 @@
     <sheet name="Addresses" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Phones" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Emails" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Contact people" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Interfaces" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Vendor info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Accounts" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="URLs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Contact people" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Interfaces" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Vendor info" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Accounts" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -162,7 +163,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -220,6 +221,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -651,7 +656,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>This applies on every sheet, not just Main Org record - e.g. PHONE on the Phones sheet, EMAIL on the Emails sheet, ACCOUNT NAME/ACCOUNT NUMBER/ACCOUNT STATUS on the Accounts sheet. One exception: an interface's USERNAME/PASSWORD (on the Interfaces sheet) aren't colored as mandatory since an interface doesn't need login credentials at all - but if you fill in either one, you must fill in both, or just that login-credentials record is skipped (the interface itself, and the rest of that organization, still build normally).</t>
+          <t>This applies on every sheet, not just Main Org record - e.g. PHONE on the Phones sheet, EMAIL on the Emails sheet, ACCOUNT NAME/ACCOUNT NUMBER/ACCOUNT STATUS on the Accounts sheet. A colored column can also be a 'required if you use this at all' pair rather than a plain single field: an interface's USERNAME/PASSWORD (on the Interfaces sheet) are both colored because if you fill in either one, you must fill in both, or just that login-credentials record is skipped (the interface itself, and the rest of that organization, still build normally). The Interfaces sheet's own NAME column, on the other hand, is intentionally NOT colored - the real FOLIO interface record has no required fields of its own, not even a name.</t>
         </is>
       </c>
     </row>
@@ -671,6 +676,96 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14.42578125" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>ORG CODE</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>PAYMENT METHOD</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>CURRENCIES</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>CLAIMING INTERVAL</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>DISCOUNT %</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>EXP ACTIVATION INTERVAL</t>
+        </is>
+      </c>
+      <c r="G1" s="27" t="inlineStr">
+        <is>
+          <t>EXP INVOICE INTERVAL</t>
+        </is>
+      </c>
+      <c r="H1" s="27" t="inlineStr">
+        <is>
+          <t>EXP RECEIPT INTERVAL</t>
+        </is>
+      </c>
+      <c r="I1" s="27" t="inlineStr">
+        <is>
+          <t>RENEWAL ACTIVATION INTERVAL</t>
+        </is>
+      </c>
+      <c r="J1" s="27" t="inlineStr">
+        <is>
+          <t>SUBSCRIPTION INTERVAL</t>
+        </is>
+      </c>
+      <c r="K1" s="27" t="inlineStr">
+        <is>
+          <t>EXPORT TO ACCOUNTING (Y/)</t>
+        </is>
+      </c>
+      <c r="L1" s="27" t="inlineStr">
+        <is>
+          <t>TAX ID</t>
+        </is>
+      </c>
+      <c r="M1" s="27" t="inlineStr">
+        <is>
+          <t>TAX %</t>
+        </is>
+      </c>
+      <c r="N1" s="27" t="inlineStr">
+        <is>
+          <t>LIABLE FOR VAT (Y/N)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -808,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" customWidth="1" style="8" min="1" max="1"/>
@@ -823,7 +918,8 @@
     <col width="17.5703125" customWidth="1" min="13" max="13"/>
     <col width="21.140625" customWidth="1" min="16" max="16"/>
     <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -931,10 +1027,19 @@
       </c>
       <c r="R5" s="28" t="inlineStr">
         <is>
-          <t>URL CATEGORY</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="n"/>
+          <t>URL NOTE</t>
+        </is>
+      </c>
+      <c r="S5" s="28" t="inlineStr">
+        <is>
+          <t>URL CATEGORIES</t>
+        </is>
+      </c>
+      <c r="T5" s="28" t="inlineStr">
+        <is>
+          <t>ORG TYPE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -1152,7 +1257,7 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1298,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1381,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -1310,6 +1415,77 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18.140625" customWidth="1" min="1" max="1"/>
+    <col width="27.140625" customWidth="1" style="8" min="2" max="2"/>
+    <col width="27.140625" customWidth="1" min="3" max="3"/>
+    <col width="30" bestFit="1" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>ORG CODE</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>E.g., ebsco</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>customerservice@ebsco.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>E.g., ebsco</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>sales@ebsco.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1355,12 +1531,12 @@
           <t>NOTES</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">PHONE </t>
         </is>
@@ -1372,7 +1548,7 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1473,7 +1649,7 @@
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
@@ -1493,12 +1669,12 @@
           <t>DELIVERY METHOD</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="31" t="inlineStr">
         <is>
           <t>USERNAME</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="31" t="inlineStr">
         <is>
           <t>PASSWORD</t>
         </is>
@@ -1573,94 +1749,4 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14.42578125" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="inlineStr">
-        <is>
-          <t>PAYMENT METHOD</t>
-        </is>
-      </c>
-      <c r="C1" s="27" t="inlineStr">
-        <is>
-          <t>CURRENCIES</t>
-        </is>
-      </c>
-      <c r="D1" s="27" t="inlineStr">
-        <is>
-          <t>CLAIMING INTERVAL</t>
-        </is>
-      </c>
-      <c r="E1" s="27" t="inlineStr">
-        <is>
-          <t>DISCOUNT %</t>
-        </is>
-      </c>
-      <c r="F1" s="27" t="inlineStr">
-        <is>
-          <t>EXP ACTIVATION INTERVAL</t>
-        </is>
-      </c>
-      <c r="G1" s="27" t="inlineStr">
-        <is>
-          <t>EXP INVOICE INTERVAL</t>
-        </is>
-      </c>
-      <c r="H1" s="27" t="inlineStr">
-        <is>
-          <t>EXP RECEIPT INTERVAL</t>
-        </is>
-      </c>
-      <c r="I1" s="27" t="inlineStr">
-        <is>
-          <t>RENEWAL ACTIVATION INTERVAL</t>
-        </is>
-      </c>
-      <c r="J1" s="27" t="inlineStr">
-        <is>
-          <t>SUBSCRIPTION INTERVAL</t>
-        </is>
-      </c>
-      <c r="K1" s="27" t="inlineStr">
-        <is>
-          <t>EXPORT TO ACCOUNTING (Y/)</t>
-        </is>
-      </c>
-      <c r="L1" s="27" t="inlineStr">
-        <is>
-          <t>TAX ID</t>
-        </is>
-      </c>
-      <c r="M1" s="27" t="inlineStr">
-        <is>
-          <t>TAX %</t>
-        </is>
-      </c>
-      <c r="N1" s="27" t="inlineStr">
-        <is>
-          <t>LIABLE FOR VAT (Y/N)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Organization_Template.xlsx
+++ b/Organization_Template.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Interfaces" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Vendor info" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Accounts" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="External note" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -896,6 +897,48 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.57" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>ORG CODE</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TYPE</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TITLE</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>CONTENTS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1491,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1523,30 +1566,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>TITLE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>NOTES</t>
         </is>
       </c>
+      <c r="E1" s="32" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
       <c r="F1" s="32" t="inlineStr">
         <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="G1" s="32" t="inlineStr">
-        <is>
           <t xml:space="preserve">PHONE </t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
@@ -1569,18 +1607,17 @@
         </is>
       </c>
       <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>jnovak@ebsco.com</t>
+        </is>
+      </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>jnovak@ebsco.com</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
           <t>555-555-5555</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Accounts receivable</t>
         </is>
@@ -1603,18 +1640,17 @@
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>mrossi@ebsco.com</t>
+        </is>
+      </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>mrossi@ebsco.com</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
           <t>555-555-5555</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Customer service</t>
         </is>
